--- a/Артефакт 1. AI Startup Canvas — Попутчик.xlsx
+++ b/Артефакт 1. AI Startup Canvas — Попутчик.xlsx
@@ -538,8 +538,8 @@
         <is>
           <t>Сегменты клиентов (ЦА)
 Пользователи (B2C):
-• Работающие 25–45 лет без времени на магазины, семьи с детьми, студенты.
-• Пожилые и маломобильные — им проще голосовое, чем приложение.
+• Работающие 25–45 лет без времени на магазины, семьи с детьми.
+• Студенты — всё заказывают с телефона, ценят дешёвую доставку и скорость.
 Магазины и кафе (B2B):
 • Локальные продуктовые, магазины бытовых товаров, кафе без своей доставки (лекарства не входят в MVP).
 Кто платит:
